--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -20982,7 +20982,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -22807,38 +22807,30 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H349" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I349" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H349" s="5" t="n">
+        <v>31486000</v>
+      </c>
+      <c r="I349" s="5" t="n">
+        <v>32901</v>
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K349" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L349" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K349" s="5" t="n">
+        <v>31486000</v>
+      </c>
+      <c r="L349" s="5" t="n">
+        <v>32901</v>
       </c>
       <c r="M349" s="3" t="inlineStr">
         <is>
@@ -22847,7 +22839,7 @@
       </c>
       <c r="N349" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32671,7 +32663,7 @@
           <t>C | 550呎 (2房)
 $1705万
 $31,000/呎
-(26年-08月-14日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -32785,7 +32777,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -32795,7 +32787,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33035,12 +33027,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 957呎 (3房)
-招标单位
--
-(在售)</t>
+$3149万
+$32,901/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -3048,7 +3048,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -29611,7 +29611,7 @@
           <t>D | 996呎 (3房)
 $3984万
 $40,000/呎
-(26年-08月-19日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -31786,7 +31786,7 @@
           <t>A | 997呎 (3房)
 $3639万
 $36,501/呎
-(26年-08月-21日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -32938,7 +32938,7 @@
           <t>A | 957呎 (3房)
 $3115万
 $32,550/呎
-(26年-08月-24日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -7317,38 +7317,30 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>36480000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>38000</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K106" s="5" t="n">
+        <v>36480000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>38000</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7357,7 +7349,7 @@
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16497,38 +16489,30 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>19654000</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>33143</v>
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K252" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L252" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K252" s="5" t="n">
+        <v>19654000</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>33143</v>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
@@ -16537,7 +16521,7 @@
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17297,38 +17281,30 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H264" s="5" t="n">
+        <v>18944000</v>
+      </c>
+      <c r="I264" s="5" t="n">
+        <v>31946</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K264" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L264" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K264" s="5" t="n">
+        <v>18944000</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>31946</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
@@ -17337,7 +17313,7 @@
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30314,7 +30290,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -30324,7 +30300,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -30376,12 +30352,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$3648万
+$38,000/呎
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -31619,7 +31595,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31629,7 +31605,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31961,12 +31937,12 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1965万
+$33,143/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -32084,12 +32060,12 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1894万
+$31,946/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -18057,38 +18057,30 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>18663000</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>31472</v>
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K276" s="5" t="n">
+        <v>18663000</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>31472</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
@@ -18097,7 +18089,7 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18321,38 +18313,30 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>18570000</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>31315</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K280" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L280" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K280" s="5" t="n">
+        <v>18570000</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>31315</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
@@ -18361,7 +18345,7 @@
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31595,7 +31579,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31605,7 +31589,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32183,12 +32167,12 @@
 (24年-04月-11日)</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1866万
+$31,472/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -32224,12 +32208,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1857万
+$31,315/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,17 +133,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -221,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,12 +279,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -678,7 +661,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -15169,7 +15152,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -15179,12 +15162,12 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J232" s="3" t="inlineStr">
@@ -15194,12 +15177,12 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
@@ -15209,7 +15192,7 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15433,7 +15416,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -15443,12 +15426,12 @@
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J236" s="3" t="inlineStr">
@@ -15458,12 +15441,12 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
@@ -15473,7 +15456,7 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15697,7 +15680,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -15707,12 +15690,12 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J240" s="3" t="inlineStr">
@@ -15722,12 +15705,12 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
@@ -15737,7 +15720,7 @@
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15952,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -15977,31 +15960,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H244" s="5" t="n">
-        <v>23743000</v>
-      </c>
-      <c r="I244" s="5" t="n">
-        <v>40039</v>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="n">
-        <v>20181550</v>
-      </c>
-      <c r="L244" s="5" t="n">
-        <v>34033</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>如「瑜」得水 120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17536,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -17553,31 +17544,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H268" s="5" t="n">
-        <v>22150000</v>
-      </c>
-      <c r="I268" s="5" t="n">
-        <v>37352</v>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K268" s="5" t="n">
-        <v>18827500</v>
-      </c>
-      <c r="L268" s="5" t="n">
-        <v>31750</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>如「瑜」得水 120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17800,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -17809,31 +17808,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H272" s="5" t="n">
-        <v>22018000</v>
-      </c>
-      <c r="I272" s="5" t="n">
-        <v>37130</v>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K272" s="5" t="n">
-        <v>18715300</v>
-      </c>
-      <c r="L272" s="5" t="n">
-        <v>31560</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>如「瑜」得水 120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -31579,12 +31586,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -31594,12 +31601,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -31716,12 +31723,12 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -31757,12 +31764,12 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -31798,12 +31805,12 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -31839,12 +31846,12 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2374万
-$40,039/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -32085,12 +32092,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2215万
-$37,352/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -32126,12 +32133,12 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$2202万
-$37,130/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -15152,38 +15152,30 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I232" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>21446000</v>
+      </c>
+      <c r="I232" s="5" t="n">
+        <v>36165</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K232" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L232" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K232" s="5" t="n">
+        <v>21446000</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>36165</v>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
@@ -15192,7 +15184,7 @@
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15416,38 +15408,30 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>20941000</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>35314</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K236" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L236" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K236" s="5" t="n">
+        <v>20941000</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>35314</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
@@ -15456,7 +15440,7 @@
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -16084,38 +16068,30 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H246" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="n">
+        <v>35975000</v>
+      </c>
+      <c r="I246" s="5" t="n">
+        <v>36083</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K246" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L246" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K246" s="5" t="n">
+        <v>35975000</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>36083</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -16124,7 +16100,7 @@
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17800,38 +17776,30 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>18756000</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>31629</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K272" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L272" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K272" s="5" t="n">
+        <v>18756000</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>31629</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17840,7 +17808,7 @@
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -21006,38 +20974,30 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H321" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I321" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H321" s="5" t="n">
+        <v>17205000</v>
+      </c>
+      <c r="I321" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K321" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L321" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K321" s="5" t="n">
+        <v>17205000</v>
+      </c>
+      <c r="L321" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
@@ -21046,7 +21006,7 @@
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31586,7 +31546,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31596,7 +31556,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31723,7 +31683,89 @@
 (26年-07月-22日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2145万
+$36,165/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3639万
+$36,501/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2152万
+$36,046/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$2094万
+$35,314/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$2154万
+$36,089/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -31731,7 +31773,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31739,32 +31781,32 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3639万
-$36,501/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+$3598万
+$36,083/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2152万
-$36,046/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
+$2022万
+$33,871/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -31772,7 +31814,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31780,16 +31822,57 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr"/>
-      <c r="G8" s="21" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3420万
+$34,301/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1990万
+$33,337/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1997万
+$33,671/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31797,15 +31880,179 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2154万
-$36,089/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
+$1959万
+$32,814/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1965万
+$33,143/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1967万
+$32,942/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1947万
+$32,832/呎
+(23年-12月-07日)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1898万
+$31,789/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1904万
+$32,106/呎
+(26年-08月-20日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1928万
+$32,295/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1894万
+$31,946/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3210万
+$32,201/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1883万
+$31,536/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -31813,7 +32060,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31821,16 +32068,262 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr"/>
-      <c r="G9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3170万
+$31,800/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1871万
+$31,347/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1876万
+$31,629/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3121万
+$31,300/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1876万
+$31,419/呎
+(24年-04月-11日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1866万
+$31,472/呎
+(26年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3071万
+$30,800/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1851万
+$31,005/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1857万
+$31,315/呎
+(26年-09月-21日)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$3021万
+$30,301/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1923万
+$32,205/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1907万
+$32,156/呎
+(23年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2971万
+$29,800/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1869万
+$31,310/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1833万
+$30,905/呎
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+$2921万
+$29,301/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1836万
+$30,960/呎
+(23年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31838,15 +32331,56 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$2022万
-$33,871/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
+$1765万
+$29,564/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 593呎 (2房)
+$1786万
+$30,117/呎
+(24年-02月-07日)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 992呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 597呎 (2房)
+$1789万
+$29,964/呎
+(23年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
 招标单位
@@ -31854,7 +32388,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31862,40 +32396,40 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr"/>
-      <c r="G10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-$3420万
-$34,301/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1990万
-$33,337/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+$1680万
+$28,141/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1997万
-$33,671/呎
-(26年-09月-01日)</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
+$1723万
+$29,047/呎
+(23年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31903,16 +32437,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr"/>
-      <c r="G11" s="21" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31920,23 +32454,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1959万
-$32,814/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+$1657万
+$27,762/呎
+(23年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1965万
-$33,143/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31944,16 +32478,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr"/>
-      <c r="G12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr"/>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -31961,23 +32495,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1967万
-$32,942/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$1581万
+$26,487/呎
+(24年-03月-22日)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1947万
-$32,832/呎
-(23年-12月-07日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
+$1624万
+$27,381/呎
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -31985,16 +32519,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr"/>
-      <c r="G13" s="21" t="inlineStr"/>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
 招标单位
@@ -32002,23 +32536,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-$1898万
-$31,789/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
+$1589万
+$26,622/呎
+(23年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-$1904万
-$32,106/呎
-(26年-08月-20日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
+$1576万
+$26,584/呎
+(23年-06月-13日)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 992呎 (3房)
 -
@@ -32026,580 +32560,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1928万
-$32,295/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1894万
-$31,946/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr"/>
-      <c r="G15" s="21" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3210万
-$32,201/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1883万
-$31,536/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr"/>
-      <c r="G16" s="21" t="inlineStr"/>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3170万
-$31,800/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1871万
-$31,347/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr"/>
-      <c r="G17" s="21" t="inlineStr"/>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3121万
-$31,300/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1876万
-$31,419/呎
-(24年-04月-11日)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1866万
-$31,472/呎
-(26年-09月-18日)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3071万
-$30,800/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1851万
-$31,005/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1857万
-$31,315/呎
-(26年-09月-21日)</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr"/>
-      <c r="G19" s="21" t="inlineStr"/>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$3021万
-$30,301/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1923万
-$32,205/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1907万
-$32,156/呎
-(23年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2971万
-$29,800/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1869万
-$31,310/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1833万
-$30,905/呎
-(23年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr"/>
-      <c r="G21" s="21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-$2921万
-$29,301/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1836万
-$30,960/呎
-(23年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1765万
-$29,564/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1786万
-$30,117/呎
-(24年-02月-07日)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr"/>
-      <c r="G23" s="21" t="inlineStr"/>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1789万
-$29,964/呎
-(23年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr"/>
-      <c r="G24" s="21" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1680万
-$28,141/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1723万
-$29,047/呎
-(23年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr"/>
-      <c r="G25" s="21" t="inlineStr"/>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1657万
-$27,762/呎
-(23年-06月-14日)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr"/>
-      <c r="G26" s="21" t="inlineStr"/>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1581万
-$26,487/呎
-(24年-03月-22日)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1624万
-$27,381/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr"/>
-      <c r="G27" s="21" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>B | 597呎 (2房)
-$1589万
-$26,622/呎
-(23年-07月-04日)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>C | 593呎 (2房)
-$1576万
-$26,584/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>D | 992呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="F28" s="21" t="inlineStr"/>
       <c r="G28" s="21" t="inlineStr"/>
     </row>
@@ -32617,12 +32577,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 555呎 (2房)
-招标单位
--
-(在售)</t>
+$1720万
+$31,000/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -17512,38 +17512,30 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="n">
+        <v>19265000</v>
+      </c>
+      <c r="I268" s="5" t="n">
+        <v>32487</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K268" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L268" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K268" s="5" t="n">
+        <v>19265000</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>32487</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
@@ -17552,7 +17544,7 @@
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19444,38 +19436,30 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H298" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I298" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H298" s="5" t="n">
+        <v>30110000</v>
+      </c>
+      <c r="I298" s="5" t="n">
+        <v>30201</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K298" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L298" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K298" s="5" t="n">
+        <v>30110000</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>30201</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
@@ -19484,7 +19468,7 @@
       </c>
       <c r="N298" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22723,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -31546,7 +31530,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31556,7 +31540,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32052,12 +32036,12 @@
 (26年-05月-06日)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 593呎 (2房)
-招标单位
--
-(在售)</t>
+$1926万
+$32,487/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -32323,12 +32307,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 997呎 (3房)
-招标单位
--
-(在售)</t>
+$3011万
+$30,201/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -32959,7 +32943,7 @@
           <t>A | 957呎 (3房)
 $3149万
 $32,901/呎
-(26年-09月-09日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -16461,7 +16461,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -31877,7 +31877,7 @@
           <t>C | 593呎 (2房)
 $1965万
 $33,143/呎
-(26年-09月-15日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
         <v>36480000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>38000</v>
+        <v>38040</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>36480000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>38000</v>
+        <v>38040</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>8627500</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>23702</v>
+        <v>23637</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>8627500</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>23702</v>
+        <v>23637</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -30289,10 +30289,10 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 960呎 (3房)
+          <t>A | 959呎 (3房)
 $3648万
-$38,000/呎
-(26年-09月-16日)</t>
+$38,040/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -31167,9 +31167,9 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>E | 364呎 (1房)
+          <t>E | 365呎 (1房)
 $863万
-$23,702/呎
+$23,637/呎
 (23年-06月-12日)</t>
         </is>
       </c>
@@ -32000,7 +32000,7 @@
           <t>C | 593呎 (2房)
 $1894万
 $31,946/呎
-(26年-09月-15日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -32123,7 +32123,7 @@
           <t>C | 593呎 (2房)
 $1866万
 $31,472/呎
-(26年-09月-18日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -18285,7 +18285,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -32164,7 +32164,7 @@
           <t>C | 593呎 (2房)
 $1857万
 $31,315/呎
-(26年-09月-21日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -15157,7 +15157,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -19110,38 +19110,30 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H293" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I293" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H293" s="5" t="n">
+        <v>18806000</v>
+      </c>
+      <c r="I293" s="5" t="n">
+        <v>31501</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K293" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L293" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K293" s="5" t="n">
+        <v>18806000</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>31501</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -19150,7 +19142,7 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -19441,7 +19433,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20954,7 +20946,7 @@
         </is>
       </c>
       <c r="E321" s="4" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
@@ -20963,14 +20955,14 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
         <v>17205000</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>31000</v>
+        <v>31056</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -20981,7 +20973,7 @@
         <v>17205000</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>31000</v>
+        <v>31056</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
@@ -25203,14 +25195,14 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
-        <v>28738600</v>
+        <v>28404400</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>30030</v>
+        <v>29681</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
@@ -25218,10 +25210,10 @@
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>28738600</v>
+        <v>28404400</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>30030</v>
+        <v>29681</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -31530,7 +31522,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31540,7 +31532,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31672,7 +31664,7 @@
           <t>C | 593呎 (2房)
 $2145万
 $36,165/呎
-(26年-09月-28日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -31713,7 +31705,7 @@
           <t>C | 593呎 (2房)
 $2094万
 $35,314/呎
-(26年-09月-28日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -31779,7 +31771,7 @@
           <t>A | 997呎 (3房)
 $3598万
 $36,083/呎
-(26年-09月-28日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -32041,7 +32033,7 @@
           <t>C | 593呎 (2房)
 $1926万
 $32,487/呎
-(26年-10月-05日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -32082,7 +32074,7 @@
           <t>C | 593呎 (2房)
 $1876万
 $31,629/呎
-(26年-09月-28日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -32274,12 +32266,12 @@
 (26年-08月-03日)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 597呎 (2房)
-招标单位
--
-(在售)</t>
+$1881万
+$31,501/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -32312,7 +32304,7 @@
           <t>A | 997呎 (3房)
 $3011万
 $30,201/呎
-(26年-10月-05日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -32563,10 +32555,10 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>B | 555呎 (2房)
+          <t>B | 554呎 (2房)
 $1720万
-$31,000/呎
-(26年-09月-28日)</t>
+$31,056/呎
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -33317,9 +33309,9 @@
       <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 957呎 (3房)
-$2874万
-$30,030/呎
-(23年-10月-09日)</t>
+$2840万
+$29,681/呎
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">

--- a/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
+++ b/九龙-何文田-瑜一．天海/瑜一．天海_销控明细表.xlsx
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>525</v>
+        <v>591</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>19086700</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>36356</v>
+        <v>32296</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>19086700</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>36356</v>
+        <v>32296</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>36480000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>38040</v>
+        <v>38000</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>36480000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>38040</v>
+        <v>38000</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>29760000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>31032</v>
+        <v>31000</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>29760000</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>31032</v>
+        <v>31000</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>28800000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>30031</v>
+        <v>30000</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>28800000</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>30031</v>
+        <v>30000</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>9103600</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>24941</v>
+        <v>25010</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>9103600</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>24941</v>
+        <v>25010</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>943</v>
+        <v>338</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>7608700</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>8069</v>
+        <v>22511</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>7608700</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>8069</v>
+        <v>22511</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>27648000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>28830</v>
+        <v>28800</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>27648000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>28830</v>
+        <v>28800</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>8968000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>24570</v>
+        <v>24637</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>8968000</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>24570</v>
+        <v>24637</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>24864000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>25927</v>
+        <v>25900</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>24864000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>25927</v>
+        <v>25900</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>8627500</v>
       </c>
       <c r="I192" s="5" t="n">
-        <v>23637</v>
+        <v>23702</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>8627500</v>
       </c>
       <c r="L192" s="5" t="n">
-        <v>23637</v>
+        <v>23702</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>8052700</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>25483</v>
+        <v>25403</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>8052700</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>25483</v>
+        <v>25403</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>28427000</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>31034</v>
+        <v>31000</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>28427000</v>
       </c>
       <c r="L226" s="5" t="n">
-        <v>31034</v>
+        <v>31000</v>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         </is>
       </c>
       <c r="E321" s="4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>17205000</v>
       </c>
       <c r="I321" s="5" t="n">
-        <v>31056</v>
+        <v>31000</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>17205000</v>
       </c>
       <c r="L321" s="5" t="n">
-        <v>31056</v>
+        <v>31000</v>
       </c>
       <c r="M321" s="3" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>13843100</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>32572</v>
+        <v>32496</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>13843100</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>32572</v>
+        <v>32496</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>47770000</v>
       </c>
       <c r="I329" s="5" t="n">
-        <v>41757</v>
+        <v>41721</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>47770000</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>41757</v>
+        <v>41721</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         </is>
       </c>
       <c r="E331" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>30639900</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>32735</v>
+        <v>32700</v>
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>30639900</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>32735</v>
+        <v>32700</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>30171400</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>32234</v>
+        <v>32200</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>30171400</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>32234</v>
+        <v>32200</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>29703000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>31734</v>
+        <v>31700</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>29703000</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>31734</v>
+        <v>31700</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>27828900</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>29732</v>
+        <v>29700</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>27828900</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>29732</v>
+        <v>29700</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>27360000</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>29231</v>
+        <v>29200</v>
       </c>
       <c r="J351" s="3" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>27360000</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>29231</v>
+        <v>29200</v>
       </c>
       <c r="M351" s="3" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>26891900</v>
       </c>
       <c r="I356" s="5" t="n">
-        <v>28731</v>
+        <v>28700</v>
       </c>
       <c r="J356" s="3" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>26891900</v>
       </c>
       <c r="L356" s="5" t="n">
-        <v>28731</v>
+        <v>28700</v>
       </c>
       <c r="M356" s="3" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>26423400</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>28230</v>
+        <v>28200</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>26423400</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>28230</v>
+        <v>28200</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>25954000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>27729</v>
+        <v>27699</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>25954000</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>27729</v>
+        <v>27699</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>24736000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>26427</v>
+        <v>26399</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>24736000</v>
       </c>
       <c r="L381" s="5" t="n">
-        <v>26427</v>
+        <v>26399</v>
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>24408850</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>26078</v>
+        <v>26050</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>24408850</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>26078</v>
+        <v>26050</v>
       </c>
       <c r="M386" s="3" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         </is>
       </c>
       <c r="E391" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>24174000</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>25827</v>
+        <v>25799</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>24174000</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>25827</v>
+        <v>25799</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="E396" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>23893500</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>25527</v>
+        <v>25500</v>
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>23893500</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>25527</v>
+        <v>25500</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="E416" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>22394300</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>23926</v>
+        <v>23900</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>22394300</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>23926</v>
+        <v>23900</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         </is>
       </c>
       <c r="E421" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>22534900</v>
       </c>
       <c r="I421" s="5" t="n">
-        <v>24076</v>
+        <v>24050</v>
       </c>
       <c r="J421" s="3" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>22534900</v>
       </c>
       <c r="L421" s="5" t="n">
-        <v>24076</v>
+        <v>24050</v>
       </c>
       <c r="M421" s="3" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         </is>
       </c>
       <c r="E426" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>21832000</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>23325</v>
+        <v>23300</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>21832000</v>
       </c>
       <c r="L426" s="5" t="n">
-        <v>23325</v>
+        <v>23300</v>
       </c>
       <c r="M426" s="3" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>21551000</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>23025</v>
+        <v>23000</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>21551000</v>
       </c>
       <c r="L431" s="5" t="n">
-        <v>23025</v>
+        <v>23000</v>
       </c>
       <c r="M431" s="3" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         </is>
       </c>
       <c r="E436" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>21691600</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>23175</v>
+        <v>23150</v>
       </c>
       <c r="J436" s="3" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>21691600</v>
       </c>
       <c r="L436" s="5" t="n">
-        <v>23175</v>
+        <v>23150</v>
       </c>
       <c r="M436" s="3" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="E441" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>21738400</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>23225</v>
+        <v>23200</v>
       </c>
       <c r="J441" s="3" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>21738400</v>
       </c>
       <c r="L441" s="5" t="n">
-        <v>23225</v>
+        <v>23200</v>
       </c>
       <c r="M441" s="3" t="inlineStr">
         <is>
@@ -29411,9 +29411,9 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 525呎 (2房)
+          <t>B | 591呎 (2房)
 $1909万
-$36,356/呎
+$32,296/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -30281,9 +30281,9 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 $3648万
-$38,040/呎
+$38,000/呎
 (26年-10月-13日)</t>
         </is>
       </c>
@@ -30328,9 +30328,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 $2976万
-$31,032/呎
+$31,000/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -30422,9 +30422,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 $2880万
-$30,031/呎
+$30,000/呎
 (25年-09月-23日)</t>
         </is>
       </c>
@@ -30595,9 +30595,9 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>E | 365呎 (1房)
+          <t>E | 364呎 (1房)
 $910万
-$24,941/呎
+$25,010/呎
 (23年-06月-13日)</t>
         </is>
       </c>
@@ -30673,9 +30673,9 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>C | 943呎 (1房)
+          <t>C | 338呎 (1房)
 $761万
-$8,069/呎
+$22,511/呎
 (25年-04月-30日)</t>
         </is>
       </c>
@@ -30704,9 +30704,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 $2765万
-$28,830/呎
+$28,800/呎
 (26年-08月-25日)</t>
         </is>
       </c>
@@ -30830,9 +30830,9 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>E | 365呎 (1房)
+          <t>E | 364呎 (1房)
 $897万
-$24,570/呎
+$24,637/呎
 (23年-07月-12日)</t>
         </is>
       </c>
@@ -30939,9 +30939,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 959呎 (3房)
+          <t>A | 960呎 (3房)
 $2486万
-$25,927/呎
+$25,900/呎
 (25年-09月-17日)</t>
         </is>
       </c>
@@ -31159,9 +31159,9 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>E | 365呎 (1房)
+          <t>E | 364呎 (1房)
 $863万
-$23,637/呎
+$23,702/呎
 (23年-06月-12日)</t>
         </is>
       </c>
@@ -31409,9 +31409,9 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>A | 916呎 (3房)
+          <t>A | 917呎 (3房)
 $2843万
-$31,034/呎
+$31,000/呎
 (26年-02月-06日)</t>
         </is>
       </c>
@@ -31425,9 +31425,9 @@
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>C | 316呎 (1房)
+          <t>C | 317呎 (1房)
 $805万
-$25,483/呎
+$25,403/呎
 (24年-08月-29日)</t>
         </is>
       </c>
@@ -32555,9 +32555,9 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>B | 554呎 (2房)
+          <t>B | 555呎 (2房)
 $1720万
-$31,056/呎
+$31,000/呎
 (26年-10月-21日)</t>
         </is>
       </c>
@@ -32744,17 +32744,17 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 1144呎 (3房)
+          <t>A | 1145呎 (3房)
 $4777万
-$41,757/呎
+$41,721/呎
 (26年-04月-27日)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>B | 425呎 (2房)
+          <t>B | 426呎 (2房)
 $1384万
-$32,572/呎
+$32,496/呎
 (25年-11月-21日)</t>
         </is>
       </c>
@@ -32815,9 +32815,9 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $3064万
-$32,735/呎
+$32,700/呎
 (26年-05月-29日)</t>
         </is>
       </c>
@@ -32862,9 +32862,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $3017万
-$32,234/呎
+$32,200/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -32909,9 +32909,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2970万
-$31,734/呎
+$31,700/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -32956,9 +32956,9 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2783万
-$29,732/呎
+$29,700/呎
 (25年-11月-12日)</t>
         </is>
       </c>
@@ -33003,9 +33003,9 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2736万
-$29,231/呎
+$29,200/呎
 (25年-10月-16日)</t>
         </is>
       </c>
@@ -33050,9 +33050,9 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2689万
-$28,731/呎
+$28,700/呎
 (25年-11月-25日)</t>
         </is>
       </c>
@@ -33097,9 +33097,9 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2642万
-$28,230/呎
+$28,200/呎
 (25年-11月-17日)</t>
         </is>
       </c>
@@ -33144,9 +33144,9 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2595万
-$27,729/呎
+$27,699/呎
 (25年-10月-24日)</t>
         </is>
       </c>
@@ -33285,9 +33285,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2474万
-$26,427/呎
+$26,399/呎
 (25年-10月-24日)</t>
         </is>
       </c>
@@ -33332,9 +33332,9 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2441万
-$26,078/呎
+$26,050/呎
 (25年-09月-09日)</t>
         </is>
       </c>
@@ -33379,9 +33379,9 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2417万
-$25,827/呎
+$25,799/呎
 (25年-09月-04日)</t>
         </is>
       </c>
@@ -33426,9 +33426,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2389万
-$25,527/呎
+$25,500/呎
 (25年-09月-16日)</t>
         </is>
       </c>
@@ -33614,9 +33614,9 @@
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2239万
-$23,926/呎
+$23,900/呎
 (25年-11月-04日)</t>
         </is>
       </c>
@@ -33661,9 +33661,9 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2253万
-$24,076/呎
+$24,050/呎
 (26年-01月-29日)</t>
         </is>
       </c>
@@ -33708,9 +33708,9 @@
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2183万
-$23,325/呎
+$23,300/呎
 (25年-11月-26日)</t>
         </is>
       </c>
@@ -33755,9 +33755,9 @@
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2155万
-$23,025/呎
+$23,000/呎
 (25年-12月-04日)</t>
         </is>
       </c>
@@ -33802,9 +33802,9 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2169万
-$23,175/呎
+$23,150/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -33849,9 +33849,9 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>D | 936呎 (3房)
+          <t>D | 937呎 (3房)
 $2174万
-$23,225/呎
+$23,200/呎
 (26年-04月-09日)</t>
         </is>
       </c>
